--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_4_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_4_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319229.1376669946</v>
+        <v>303475.5431129429</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>3013503.893776012</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.1449482</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813755.887318158</v>
+        <v>4790382.659738131</v>
       </c>
     </row>
     <row r="11">
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1211,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1366,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1557,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.95151064538747</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1603,22 +1603,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>12.35200489467393</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>14.67170078545518</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1925,16 +1925,16 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>23.91580867374213</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.02246762618611</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2043,19 +2043,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>230.2038249569697</v>
       </c>
       <c r="Y20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -2156,22 +2156,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>78.32097487848354</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2198,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>104.6829309709404</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -2277,19 +2277,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2350,22 +2350,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>41.69029206467251</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>87.15362579653082</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
@@ -2399,16 +2399,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>185.9169747726711</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>62.4162677022923</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>110.3566704350806</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -2669,25 +2669,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>37.96185577332633</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2836,19 +2836,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>97.71100824342165</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2912,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>84.47684708846108</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2952,55 +2952,55 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3016,31 +3016,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>189.372</v>
+        <v>220.8837963815378</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>90.16983368421225</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>40.63654404309288</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3146,25 +3146,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3265,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>234.288905720311</v>
       </c>
     </row>
     <row r="36">
@@ -3332,22 +3332,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>45.9962868328712</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3383,25 +3383,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>56.91690033700354</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3547,19 +3547,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>222.3396163656984</v>
       </c>
       <c r="W38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>185.3612311992098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>109.7364879284881</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>17.68882889616215</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -3736,19 +3736,19 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
-        <v>177.6197007854553</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>213</v>
+        <v>190.9324654410926</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>19.27312481467103</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>148.921970271393</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>48.72581743928635</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.46319117666009</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92.93786803496215</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>92.93786803496215</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>92.93786803496215</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>66.67524177233588</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>81.62201144066449</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>55.35938517803824</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09675891541198</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.834132652785714</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>28.84</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N17" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>45.34272806611634</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>17.05989978328806</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>59.55978921844228</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>31.276960935614</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.994132652785714</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M18" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="N18" t="n">
-        <v>57.68</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="O18" t="n">
-        <v>85.40000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>83.71717171717171</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>83.71717171717171</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="U19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="W19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="X19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="Y19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C20" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>738.7078125165641</v>
       </c>
       <c r="X20" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y20" t="n">
-        <v>477.1313131313132</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>588.0815197256143</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>588.0815197256143</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>588.0815197256143</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>383.2275600578374</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>621.8175600578375</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O21" t="n">
-        <v>860.4075600578375</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>125.0203343140812</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.28</v>
+        <v>756.2968567456824</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G23" t="n">
-        <v>231.8819086569757</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H23" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>742.7770012113231</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>517.427658217251</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U23" t="n">
-        <v>273.9933147829075</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="W23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y23" t="n">
-        <v>231.8819086569757</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>756.2397012350461</v>
+        <v>325.0531560887832</v>
       </c>
       <c r="C24" t="n">
-        <v>756.2397012350461</v>
+        <v>325.0531560887832</v>
       </c>
       <c r="D24" t="n">
-        <v>668.2057357840049</v>
+        <v>325.0531560887832</v>
       </c>
       <c r="E24" t="n">
-        <v>508.9682807785495</v>
+        <v>165.8157010833278</v>
       </c>
       <c r="F24" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>65.58652238664914</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M24" t="n">
-        <v>304.1765223866491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>964</v>
+        <v>776.2622314978371</v>
       </c>
       <c r="W24" t="n">
-        <v>964</v>
+        <v>532.8134548537371</v>
       </c>
       <c r="X24" t="n">
-        <v>964</v>
+        <v>532.8134548537371</v>
       </c>
       <c r="Y24" t="n">
-        <v>756.2397012350461</v>
+        <v>325.0531560887832</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>477.1313131313132</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="C26" t="n">
-        <v>233.6969696969697</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D26" t="n">
-        <v>233.6969696969697</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="Y26" t="n">
-        <v>720.5656565656566</v>
+        <v>812.6742080953335</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>307.8562975263334</v>
+        <v>481.7099827492369</v>
       </c>
       <c r="C27" t="n">
-        <v>133.4032682452064</v>
+        <v>481.7099827492369</v>
       </c>
       <c r="D27" t="n">
-        <v>133.4032682452064</v>
+        <v>481.7099827492369</v>
       </c>
       <c r="E27" t="n">
-        <v>133.4032682452064</v>
+        <v>481.7099827492369</v>
       </c>
       <c r="F27" t="n">
-        <v>133.4032682452064</v>
+        <v>335.1754247761219</v>
       </c>
       <c r="G27" t="n">
-        <v>133.4032682452064</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N27" t="n">
-        <v>613.1906659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>851.7806659261865</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>761.813405358766</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="U27" t="n">
-        <v>761.813405358766</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="V27" t="n">
-        <v>723.4680964968202</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="W27" t="n">
-        <v>723.4680964968202</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="X27" t="n">
-        <v>515.6165962912874</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="Y27" t="n">
-        <v>307.8562975263334</v>
+        <v>481.7099827492369</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>710.516763498309</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>467.067986854209</v>
       </c>
       <c r="W29" t="n">
-        <v>720.5656565656566</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="X29" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y29" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>117.9779881246683</v>
+        <v>502.6601697108322</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>328.2071404297052</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>179.2727307684539</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>65.58652238664914</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M30" t="n">
-        <v>304.1765223866491</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>533.5897870951551</v>
+        <v>878.7270069364331</v>
       </c>
       <c r="V30" t="n">
-        <v>533.5897870951551</v>
+        <v>878.7270069364331</v>
       </c>
       <c r="W30" t="n">
-        <v>533.5897870951551</v>
+        <v>878.7270069364331</v>
       </c>
       <c r="X30" t="n">
-        <v>325.7382868896223</v>
+        <v>670.8755067309003</v>
       </c>
       <c r="Y30" t="n">
-        <v>117.9779881246683</v>
+        <v>670.8755067309003</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>451.5434343434343</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="C32" t="n">
-        <v>451.5434343434343</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="D32" t="n">
-        <v>451.5434343434343</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="E32" t="n">
-        <v>451.5434343434343</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>112.0246760654541</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>292.1005276501127</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W32" t="n">
-        <v>860</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X32" t="n">
-        <v>668.7151515151515</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="Y32" t="n">
-        <v>668.7151515151515</v>
+        <v>487.4018176583718</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G33" t="n">
-        <v>59.00114683772802</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>221.45</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>434.3</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N33" t="n">
-        <v>647.15</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U33" t="n">
-        <v>642.8282828282828</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V33" t="n">
-        <v>642.8282828282828</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="W33" t="n">
-        <v>642.8282828282828</v>
+        <v>318.9674160535941</v>
       </c>
       <c r="X33" t="n">
-        <v>434.97678262275</v>
+        <v>111.1159158480613</v>
       </c>
       <c r="Y33" t="n">
-        <v>227.216483857796</v>
+        <v>111.1159158480613</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y34" t="n">
-        <v>151.7322904902707</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>451.5434343434343</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="U35" t="n">
-        <v>849.9083846317729</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="V35" t="n">
-        <v>849.9083846317729</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="W35" t="n">
-        <v>668.7151515151515</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="X35" t="n">
-        <v>668.7151515151515</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="Y35" t="n">
-        <v>668.7151515151515</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>518.3673184306008</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>518.3673184306008</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>369.4329087693495</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>210.195453763894</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>63.66089579077899</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>355.4075600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>464.5065223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N36" t="n">
-        <v>464.5065223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O36" t="n">
-        <v>677.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>686.5826554506689</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V36" t="n">
-        <v>686.5826554506689</v>
+        <v>678.3417187247995</v>
       </c>
       <c r="W36" t="n">
-        <v>686.5826554506689</v>
+        <v>434.8929420806995</v>
       </c>
       <c r="X36" t="n">
-        <v>686.5826554506689</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y36" t="n">
-        <v>686.5826554506689</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="C38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="E38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S38" t="n">
-        <v>638.7770012113231</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T38" t="n">
-        <v>638.7770012113231</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="U38" t="n">
-        <v>421.6052840396059</v>
+        <v>499.3853800778592</v>
       </c>
       <c r="V38" t="n">
-        <v>421.6052840396059</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="W38" t="n">
-        <v>204.4335668678887</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="X38" t="n">
-        <v>204.4335668678887</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="Y38" t="n">
-        <v>17.2</v>
+        <v>274.7999090013961</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>279.0604900729671</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>279.0604900729671</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>130.1260804117159</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>130.1260804117159</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>130.1260804117159</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M39" t="n">
-        <v>464.5065223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N39" t="n">
-        <v>464.5065223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O39" t="n">
-        <v>677.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T39" t="n">
-        <v>686.5826554506689</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U39" t="n">
-        <v>469.4109382789517</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V39" t="n">
-        <v>252.2392211072345</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="W39" t="n">
-        <v>35.06750393551732</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="X39" t="n">
-        <v>17.2</v>
+        <v>655.0361258579891</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>447.2758270930352</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="C41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="D41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="E41" t="n">
-        <v>626.7568694802578</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="F41" t="n">
-        <v>411.6053543287427</v>
+        <v>422.536925949487</v>
       </c>
       <c r="G41" t="n">
-        <v>232.1915151515151</v>
+        <v>422.536925949487</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="X41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="Y41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>17.04</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="C42" t="n">
-        <v>17.04</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="D42" t="n">
-        <v>17.04</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="E42" t="n">
-        <v>17.04</v>
+        <v>416.4625927250934</v>
       </c>
       <c r="F42" t="n">
-        <v>17.04</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="G42" t="n">
-        <v>17.04</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>228.3639620705569</v>
       </c>
       <c r="N42" t="n">
-        <v>564.1375600578374</v>
+        <v>439.6539830517264</v>
       </c>
       <c r="O42" t="n">
-        <v>775.0075600578374</v>
+        <v>650.9440040328959</v>
       </c>
       <c r="P42" t="n">
-        <v>852</v>
+        <v>833.5874816462467</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>750.8304705528857</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>577.4131260035546</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>375.2265313623206</v>
+        <v>651.5104598281378</v>
       </c>
       <c r="U42" t="n">
-        <v>375.2265313623206</v>
+        <v>651.5104598281378</v>
       </c>
       <c r="V42" t="n">
-        <v>375.2265313623206</v>
+        <v>651.5104598281378</v>
       </c>
       <c r="W42" t="n">
-        <v>224.8002987649539</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="X42" t="n">
-        <v>224.8002987649539</v>
+        <v>435.9303955681954</v>
       </c>
       <c r="Y42" t="n">
-        <v>17.04</v>
+        <v>435.9303955681954</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>151.6062315796582</v>
       </c>
     </row>
     <row r="44">
@@ -8433,10 +8433,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
@@ -8445,10 +8445,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,7 +8512,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
         <v>138.5543797798742</v>
@@ -8521,13 +8521,13 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>156.2912070328283</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
         <v>139.9817740860215</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,16 +8670,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
         <v>230.0982114216867</v>
@@ -8755,19 +8755,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,19 +8907,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
         <v>231.2329957552695</v>
@@ -8992,16 +8992,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>246.9585379136674</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7664149699872</v>
+        <v>262.2416917349371</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9229,19 +9229,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>160.8430942830171</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9393,7 +9393,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O20" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
         <v>321.7987081714826</v>
@@ -9463,19 +9463,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P21" t="n">
-        <v>168.5177219889092</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
         <v>210.0772877358491</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>185.3286448168935</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9937,19 +9937,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>177.2317564653243</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
         <v>210.0772877358491</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10174,22 +10174,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>185.3286448168935</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>315.8723521211968</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,19 +10408,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>344.8675110930055</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
@@ -10566,16 +10566,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
-        <v>338.5081515458031</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
         <v>380.8001812627454</v>
@@ -10648,16 +10648,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>252.3350059713232</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10885,16 +10885,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>252.3350059713232</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.6438299680839</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>211.74454877005</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>160.2944739073598</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>238.4355521223813</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23069,19 +23069,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23224,16 +23224,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>359.0295700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
         <v>210.4758895704059</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23415,19 +23415,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>371.7823310180931</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
@@ -23461,22 +23461,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>355.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23625,19 +23625,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>394.5240408470375</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>236.6739521223813</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,16 +23783,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>113.4277084894685</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>84.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>61.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>72.15783415264313</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23847,13 +23847,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>157.8095125557512</v>
+        <v>152.2419549216212</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
       </c>
       <c r="D19" t="n">
-        <v>148.6154730182124</v>
+        <v>126.1667136577029</v>
       </c>
       <c r="E19" t="n">
         <v>146.4339626465692</v>
@@ -23901,19 +23901,19 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>199.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>197.7096553890372</v>
+        <v>198.119630128721</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23938,10 +23938,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>194.6032457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23980,7 +23980,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -23992,10 +23992,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>139.5272757214993</v>
       </c>
       <c r="Y20" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,7 +24005,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>172.7084989883157</v>
@@ -24014,22 +24014,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>79.3241055769174</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24056,25 +24056,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>147.0120521899792</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24147,7 +24147,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24208,22 +24208,22 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U23" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>286.0619664054624</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W23" t="n">
         <v>349.240968717413</v>
@@ -24248,7 +24248,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>60.29143976810792</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -24257,16 +24257,16 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24302,10 +24302,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>46.88361237675414</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24400,19 +24400,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>302.8566240687152</v>
       </c>
       <c r="D26" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
-        <v>169.6575700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24448,7 +24448,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24482,7 +24482,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24491,16 +24491,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>26.98684672812999</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,25 +24527,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>194.8387313760989</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I28" t="n">
         <v>155.4504749272583</v>
@@ -24627,7 +24627,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y28" t="n">
-        <v>85.3976857667268</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="29">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>170.4610416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24649,7 +24649,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24694,19 +24694,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>167.4364142495718</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,16 +24716,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>74.99749074489409</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24770,10 +24770,10 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>141.4645349925137</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24785,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24810,7 +24810,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>34.80401177309076</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
         <v>162.2271725074396</v>
@@ -24858,7 +24858,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
@@ -24874,31 +24874,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
@@ -24937,10 +24937,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>180.3591006784691</v>
+        <v>148.8473042969312</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>76.36334996565509</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
@@ -24971,7 +24971,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>71.59890019340358</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25004,25 +25004,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25035,7 +25035,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C34" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D34" t="n">
         <v>148.6154730182124</v>
@@ -25044,7 +25044,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756325</v>
       </c>
       <c r="G34" t="n">
         <v>167.9909793584588</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25123,10 +25123,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25162,7 +25162,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>223.0958495641314</v>
@@ -25174,13 +25174,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>169.8596679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>151.9490329357426</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>91.34723033033944</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -25241,25 +25241,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>175.8836868124217</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25290,7 +25290,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I37" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -25320,7 +25320,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
         <v>227.9455894282815</v>
@@ -25363,7 +25363,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25372,7 +25372,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25405,19 +25405,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>36.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>105.4126421044365</v>
       </c>
       <c r="W38" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>200.8767074568438</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25427,13 +25427,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -25442,7 +25442,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>27.60702923472253</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>188.0841563073153</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25521,7 +25521,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
@@ -25566,7 +25566,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
         <v>286.522998336591</v>
@@ -25594,19 +25594,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>168.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>193.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
-        <v>237.6830367296798</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>126.4748021157671</v>
+        <v>148.5423366746745</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,7 +25642,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>251.3456529078365</v>
+        <v>37.92138929049358</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25673,22 +25673,22 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>138.3719556407299</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,10 +25712,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25727,13 +25727,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>102.7730128895266</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25752,7 +25752,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F43" t="n">
         <v>145.4210480229312</v>
@@ -25797,7 +25797,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350379.9730845935</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350379.9730845935</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350379.9730845937</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352026.7318511436</v>
+        <v>351700.8745024338</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>507017.9003687723</v>
+        <v>507028.2310008515</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>507017.9003687723</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>507017.9003687725</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488220.3124503887</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488220.3124503887</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488220.3124503887</v>
+        <v>507028.2310008513</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486774.3441489746</v>
+        <v>487081.0800200352</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="C2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="E2" t="n">
+        <v>69879.81359544014</v>
+      </c>
+      <c r="F2" t="n">
         <v>69879.81359544017</v>
       </c>
-      <c r="C2" t="n">
-        <v>69879.81359544015</v>
-      </c>
-      <c r="D2" t="n">
-        <v>74664.77104961485</v>
-      </c>
-      <c r="E2" t="n">
-        <v>74664.77104961486</v>
-      </c>
-      <c r="F2" t="n">
-        <v>74664.77104961486</v>
-      </c>
       <c r="G2" t="n">
-        <v>75015.25300292441</v>
+        <v>74945.90033124233</v>
       </c>
       <c r="H2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="I2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="J2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="K2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="L2" t="n">
-        <v>104001.521742606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="M2" t="n">
-        <v>104001.521742606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="N2" t="n">
-        <v>104001.521742606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="O2" t="n">
-        <v>103693.774302606</v>
+        <v>103759.0573236673</v>
       </c>
       <c r="P2" t="n">
         <v>69879.81359544017</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="D4" t="n">
-        <v>23026.20207384747</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="E4" t="n">
-        <v>23026.20207384747</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="F4" t="n">
-        <v>23026.20207384748</v>
+        <v>23035.7779262594</v>
       </c>
       <c r="G4" t="n">
-        <v>23137.88272891696</v>
+        <v>24763.57099960299</v>
       </c>
       <c r="H4" t="n">
-        <v>33649.14617662696</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="I4" t="n">
-        <v>33649.14617662695</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="J4" t="n">
-        <v>33649.14617662696</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="K4" t="n">
-        <v>33649.14617662695</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="L4" t="n">
-        <v>32374.32258066736</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="M4" t="n">
-        <v>32374.32258066736</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="N4" t="n">
-        <v>32374.32258066736</v>
+        <v>36038.21233542147</v>
       </c>
       <c r="O4" t="n">
-        <v>32276.25922713201</v>
+        <v>34590.32203425346</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>23035.7779262594</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>13216.43566918074</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915087</v>
+        <v>13216.43566918074</v>
       </c>
       <c r="D6" t="n">
-        <v>8353.788975767369</v>
+        <v>13216.43566918074</v>
       </c>
       <c r="E6" t="n">
-        <v>50057.76897576739</v>
+        <v>46844.03566918074</v>
       </c>
       <c r="F6" t="n">
-        <v>50057.76897576738</v>
+        <v>46844.03566918077</v>
       </c>
       <c r="G6" t="n">
-        <v>49626.80027400745</v>
+        <v>40942.84372233837</v>
       </c>
       <c r="H6" t="n">
-        <v>2230.975285979079</v>
+        <v>-271.2310961487965</v>
       </c>
       <c r="I6" t="n">
-        <v>59700.29228597907</v>
+        <v>57312.55604618289</v>
       </c>
       <c r="J6" t="n">
-        <v>59700.29228597907</v>
+        <v>57312.5560461829</v>
       </c>
       <c r="K6" t="n">
-        <v>59700.29228597906</v>
+        <v>57312.5560461829</v>
       </c>
       <c r="L6" t="n">
-        <v>58555.19916193867</v>
+        <v>57312.55604618292</v>
       </c>
       <c r="M6" t="n">
-        <v>58555.19916193868</v>
+        <v>57312.55604618294</v>
       </c>
       <c r="N6" t="n">
-        <v>58555.19916193868</v>
+        <v>57312.55604618293</v>
       </c>
       <c r="O6" t="n">
-        <v>58467.11507547403</v>
+        <v>56192.54006147937</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>46844.03566918077</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26904,10 +26904,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,13 +26944,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26959,34 +26959,34 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,10 +35088,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35100,10 +35100,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,7 +35167,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -35176,13 +35176,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,16 +35325,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35410,19 +35410,19 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,19 +35562,19 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35647,16 +35647,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35884,19 +35884,19 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>26.86868686868686</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36048,7 +36048,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O20" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
         <v>90.5657124162131</v>
@@ -36118,19 +36118,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P21" t="n">
-        <v>34.54331457457896</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>70.09551364982758</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>46.77426503701933</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36592,19 +36592,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>43.25734905099405</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
         <v>70.09551364982758</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36829,22 +36829,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>46.77426503701933</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>95.78250107621625</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,19 +37063,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>206.3131313131313</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -37227,10 +37227,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
-        <v>109.0950879492122</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
         <v>150.7019698410586</v>
@@ -37303,16 +37303,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>110.2009720493049</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37540,16 +37540,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>110.2009720493049</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>77.7701413557198</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>20.31269982133833</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
